--- a/public/管理口径原因分析默认模版/常州项目部.xlsx
+++ b/public/管理口径原因分析默认模版/常州项目部.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="116">
   <si>
     <t>工作表目录</t>
   </si>
@@ -48,7 +48,7 @@
     <t>常州酒店项目部销售费用</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -97,10 +97,10 @@
     <t>一、 营业收入</t>
   </si>
   <si>
-    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。酒店收入增加153万元，能源转售收入增加77万元。</t>
-  </si>
-  <si>
-    <t>客房收入减少97万元，主要是团队收入远低于预算；餐饮收入减少109万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少37万元，其他收入减少5万元</t>
+    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。收入增加114万元，客房收入增加53万元，租赁收入增加105万元，租赁收入增加为桔子和影音酒店的合作经营加入影响。</t>
+  </si>
+  <si>
+    <t>客房收入减少108万元，主要是团队收入远低于预算；餐饮收入减少138万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少50万元，有 到期退租及未租区域</t>
   </si>
   <si>
     <t xml:space="preserve">     减:（一）经营性采购支出</t>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">            其中：（1）食材耗用</t>
   </si>
   <si>
-    <t>酒店比上年同期减少餐饮食材采购18万元</t>
+    <t>比上年同期减少餐饮食材采购</t>
   </si>
   <si>
     <t>减少食品的消耗</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">                      （2）物料消耗</t>
   </si>
   <si>
-    <t>酒店比上年同期减少客用品消耗</t>
+    <t>比上年同期减少客用品消耗</t>
   </si>
   <si>
     <t>客房收入缺口大，消耗品也少于预期</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">                      （4）其他材料</t>
   </si>
   <si>
-    <t>酒店比上年同期减少商品成本</t>
+    <t>比上年同期减少商品成本</t>
   </si>
   <si>
     <t>增加的主要是床垫、防毒面罩、应急手电等低值易耗品及销售商品成本</t>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">                  2.外购燃料</t>
   </si>
   <si>
-    <t>酒店上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
+    <t>上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
   </si>
   <si>
     <t>本年度气温较往年较低，空调开启时段加长，用气量增加</t>
@@ -151,7 +151,7 @@
     <t xml:space="preserve">                  3.外购动力</t>
   </si>
   <si>
-    <t>酒店上年同期1-2月未经营，动力随经营收入增加能耗，且设备运行效率偏低，能耗率高。同时由于桔子和影音酒店的合作经营加入影响，租户能耗整体增加。</t>
+    <t>螺杆机控温方式以降低电耗，日常节能措施略有成效</t>
   </si>
   <si>
     <t>收入未达预期带来的能耗减少</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">        （六）外包劳务支出</t>
   </si>
   <si>
-    <t>其中上年同期劳务派遣转为外包人工，较同期增加餐饮业务外包费用累计40万元，增加销售外包人员共计16万元</t>
+    <t>其中上年同期劳务派遣转为外包人工，较同期增加餐饮业务外包费用累计50万元，增加销售外包人员共计19万元,增加4个配餐项目人工。</t>
   </si>
   <si>
     <t>其中主要是餐饮收入减少带来的餐饮业务外包费用减少</t>
@@ -202,10 +202,10 @@
     <t xml:space="preserve">        （七）维修费</t>
   </si>
   <si>
-    <t>增加隐患类整改14万元，大堂、二楼装饰改造工程10.89万元</t>
-  </si>
-  <si>
-    <t>增加隐患类整改14万元，</t>
+    <t>增加隐患类整改42万元，大堂、二楼装饰改造工程10.89万元。</t>
+  </si>
+  <si>
+    <t>增加隐患类整改42万元，</t>
   </si>
   <si>
     <t xml:space="preserve">        （八）租赁费</t>
@@ -214,6 +214,9 @@
     <t xml:space="preserve">        （九）物业采暖费</t>
   </si>
   <si>
+    <t>当降低团队布草更换频率及布草配置以下降洗涤费用</t>
+  </si>
+  <si>
     <t>客房出租率减少，布草洗涤量减少；适当降低团队布草更换频率及布草配置以下降洗涤费用</t>
   </si>
   <si>
@@ -250,7 +253,7 @@
     <t xml:space="preserve">        （十四）其他固定成本</t>
   </si>
   <si>
-    <t>减少为上年6月暂估的餐饮费用24万元</t>
+    <t>减少财产保险4万元</t>
   </si>
   <si>
     <t>减少财产保险4万元，审计费1.6万元，销售推广费7.7</t>
@@ -309,6 +312,9 @@
     <t xml:space="preserve">        （二十一）营业外收支净额（收益为“-”）</t>
   </si>
   <si>
+    <t>地铁影响的补偿7.95万元及减少资产报废损失</t>
+  </si>
+  <si>
     <t>地铁影响的补偿7.95万元</t>
   </si>
   <si>
@@ -333,28 +339,10 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>常州酒店预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。收入增加153万元，客房收入增加45万元，租赁收入增加112万元，租赁收入增加为桔子和影音酒店的合作经营加入影响。</t>
-  </si>
-  <si>
-    <t>比上年同期减少餐饮食材采购</t>
-  </si>
-  <si>
-    <t>比上年同期减少客用品消耗</t>
-  </si>
-  <si>
-    <t>比上年同期减少商品成本</t>
-  </si>
-  <si>
-    <t>上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
-  </si>
-  <si>
-    <t>上年同期1-2月未经营，动力随经营收入增加能耗，且设备运行效率偏低，能耗率高</t>
-  </si>
-  <si>
-    <t>江苏常州酒店能源转售预算执行分析（2026年07月）</t>
+    <t>常州酒店预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>江苏常州酒店能源转售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>能源转售收入为桔子和影音酒店的合作经营加入影响。</t>
@@ -366,10 +354,40 @@
     <t>随收入的增加，能耗也相应增加</t>
   </si>
   <si>
-    <t>江苏常州销售分公司配餐项目预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>常州酒店项目部销售费用预算执行分析（2026年07月）</t>
+    <t>随收入的增加，附加税相应增加</t>
+  </si>
+  <si>
+    <t>抵扣额增加</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收入带来的利润影响 </t>
+  </si>
+  <si>
+    <t>江苏常州销售分公司配餐项目预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>增加服务费</t>
+  </si>
+  <si>
+    <t>减少加班服务费</t>
+  </si>
+  <si>
+    <t>随收入增加而增加附加税</t>
+  </si>
+  <si>
+    <t>整体增值税按收入分摊的附加税减少</t>
+  </si>
+  <si>
+    <t>增加外包费用</t>
+  </si>
+  <si>
+    <t>减少办公费</t>
+  </si>
+  <si>
+    <t>人工成本增加影响利润</t>
+  </si>
+  <si>
+    <t>常州酒店项目部销售费用预算执行分析（2026年08月）</t>
   </si>
 </sst>
 </file>
@@ -379,7 +397,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -468,6 +486,13 @@
       <sz val="14"/>
       <name val="方正仿宋_GBK"/>
     </font>
+    <font>
+      <charset val="134"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -529,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,10 +588,13 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -594,6 +622,21 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1021,7 +1064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="168.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
@@ -1052,9 +1095,9 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -1070,9 +1113,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -1088,11 +1131,11 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="14" t="s">
         <v>30</v>
       </c>
       <c r="J6" s="11"/>
@@ -1110,11 +1153,11 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="11"/>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="J7" s="11"/>
@@ -1132,9 +1175,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -1150,11 +1193,11 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="14" t="s">
         <v>36</v>
       </c>
       <c r="H9" s="11"/>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="11"/>
@@ -1172,11 +1215,11 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>39</v>
       </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="14" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="11"/>
@@ -1185,7 +1228,7 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1194,11 +1237,11 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="14" t="s">
         <v>42</v>
       </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="14" t="s">
         <v>43</v>
       </c>
       <c r="J11" s="11"/>
@@ -1216,9 +1259,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1234,9 +1277,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1252,11 +1295,11 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="11"/>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J14" s="11"/>
@@ -1274,11 +1317,11 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="14" t="s">
         <v>49</v>
       </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="14" t="s">
         <v>50</v>
       </c>
       <c r="J15" s="11"/>
@@ -1296,9 +1339,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -1306,7 +1349,7 @@
       <c r="N16" s="11"/>
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="11"/>
@@ -1314,11 +1357,11 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="14" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="14" t="s">
         <v>54</v>
       </c>
       <c r="J17" s="11"/>
@@ -1327,8 +1370,8 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" ht="131.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="11"/>
@@ -1336,11 +1379,11 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>56</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="J18" s="11"/>
@@ -1350,7 +1393,7 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="11"/>
@@ -1358,11 +1401,11 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="14" t="s">
         <v>59</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J19" s="11"/>
@@ -1372,7 +1415,7 @@
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="11"/>
@@ -1380,9 +1423,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -1390,7 +1433,7 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="11"/>
@@ -1398,10 +1441,12 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="14" t="s">
+        <v>63</v>
+      </c>
       <c r="H21" s="11"/>
-      <c r="I21" s="12" t="s">
-        <v>63</v>
+      <c r="I21" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -1410,19 +1455,19 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>64</v>
+      <c r="A22" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
-        <v>65</v>
+      <c r="G22" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -1430,20 +1475,20 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>66</v>
+      <c r="A23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12" t="s">
-        <v>67</v>
+      <c r="G23" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12" t="s">
-        <v>67</v>
+      <c r="I23" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1452,20 +1497,20 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>68</v>
+      <c r="A24" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12" t="s">
-        <v>69</v>
+      <c r="G24" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="H24" s="11"/>
-      <c r="I24" s="12" t="s">
-        <v>70</v>
+      <c r="I24" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1474,20 +1519,20 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>71</v>
+      <c r="A25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
-        <v>72</v>
+      <c r="G25" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="H25" s="11"/>
-      <c r="I25" s="12" t="s">
-        <v>73</v>
+      <c r="I25" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1496,20 +1541,20 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>74</v>
+      <c r="A26" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
-        <v>75</v>
+      <c r="G26" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
-        <v>76</v>
+      <c r="I26" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1519,16 +1564,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -1537,19 +1582,19 @@
     </row>
     <row r="28" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12" t="s">
-        <v>79</v>
+      <c r="G28" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="H28" s="11"/>
-      <c r="I28" s="12" t="s">
-        <v>80</v>
+      <c r="I28" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1558,17 +1603,17 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>81</v>
+      <c r="A29" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -1576,20 +1621,20 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>82</v>
+      <c r="A30" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12" t="s">
-        <v>83</v>
+      <c r="G30" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="H30" s="11"/>
-      <c r="I30" s="12" t="s">
-        <v>84</v>
+      <c r="I30" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1598,17 +1643,17 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>85</v>
+      <c r="A31" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -1616,17 +1661,17 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>86</v>
+      <c r="A32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
@@ -1634,38 +1679,38 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>87</v>
+      <c r="A33" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
     </row>
-    <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>88</v>
+    <row r="34" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12" t="s">
-        <v>89</v>
+      <c r="G34" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="12" t="s">
-        <v>89</v>
+      <c r="I34" s="14" t="s">
+        <v>91</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1674,17 +1719,17 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -1692,20 +1737,20 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>91</v>
+      <c r="A36" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12" t="s">
-        <v>92</v>
+      <c r="G36" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="H36" s="11"/>
-      <c r="I36" s="12" t="s">
-        <v>92</v>
+      <c r="I36" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1714,17 +1759,17 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>93</v>
+      <c r="A37" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
@@ -1732,17 +1777,17 @@
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>94</v>
+      <c r="A38" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -1750,17 +1795,17 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>95</v>
+      <c r="A39" s="22" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
@@ -1768,17 +1813,17 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>96</v>
+      <c r="A40" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="14"/>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -1798,7 +1843,7 @@
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
     <col min="10" max="14" width="15" customWidth="1"/>
@@ -1806,7 +1851,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1866,27 +1911,27 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="168.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="150" customHeight="1" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
       <c r="G3" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="H3" s="26"/>
       <c r="I3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1897,9 +1942,9 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -1915,9 +1960,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -1933,11 +1978,11 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12" t="s">
+      <c r="G6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="27"/>
+      <c r="I6" s="14" t="s">
         <v>30</v>
       </c>
       <c r="J6" s="11"/>
@@ -1955,11 +2000,11 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12" t="s">
+      <c r="G7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="27"/>
+      <c r="I7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="J7" s="11"/>
@@ -1977,9 +2022,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -1990,16 +2035,16 @@
       <c r="A9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="27"/>
+      <c r="I9" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="11"/>
@@ -2008,7 +2053,7 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>38</v>
       </c>
@@ -2017,11 +2062,11 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
+      <c r="G10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="27"/>
+      <c r="I10" s="14" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="11"/>
@@ -2030,7 +2075,7 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -2039,11 +2084,11 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
+      <c r="G11" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="27"/>
+      <c r="I11" s="14" t="s">
         <v>43</v>
       </c>
       <c r="J11" s="11"/>
@@ -2061,9 +2106,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -2079,9 +2124,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -2097,11 +2142,11 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="27"/>
+      <c r="I14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J14" s="11"/>
@@ -2119,11 +2164,11 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="27"/>
+      <c r="I15" s="14" t="s">
         <v>50</v>
       </c>
       <c r="J15" s="11"/>
@@ -2141,9 +2186,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -2151,7 +2196,7 @@
       <c r="N16" s="11"/>
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="11"/>
@@ -2159,11 +2204,11 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
+      <c r="H17" s="27"/>
+      <c r="I17" s="14" t="s">
         <v>54</v>
       </c>
       <c r="J17" s="11"/>
@@ -2173,7 +2218,7 @@
       <c r="N17" s="11"/>
     </row>
     <row r="18" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="11"/>
@@ -2181,11 +2226,11 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12" t="s">
+      <c r="H18" s="27"/>
+      <c r="I18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="J18" s="11"/>
@@ -2195,7 +2240,7 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="11"/>
@@ -2203,11 +2248,11 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12" t="s">
+      <c r="H19" s="27"/>
+      <c r="I19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J19" s="11"/>
@@ -2217,7 +2262,7 @@
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="11"/>
@@ -2225,9 +2270,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -2235,18 +2280,20 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="14" t="s">
         <v>63</v>
+      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -2254,20 +2301,20 @@
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
     </row>
-    <row r="22" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
+    <row r="22" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="27"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -2275,20 +2322,20 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>66</v>
+      <c r="A23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12" t="s">
-        <v>67</v>
+      <c r="G23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="27"/>
+      <c r="I23" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -2297,20 +2344,20 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>68</v>
+      <c r="A24" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12" t="s">
+      <c r="G24" s="14" t="s">
         <v>70</v>
+      </c>
+      <c r="H24" s="27"/>
+      <c r="I24" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -2319,20 +2366,20 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>71</v>
+      <c r="A25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="14" t="s">
         <v>73</v>
+      </c>
+      <c r="H25" s="27"/>
+      <c r="I25" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -2341,20 +2388,20 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>74</v>
+      <c r="A26" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
+      <c r="G26" s="14" t="s">
         <v>76</v>
+      </c>
+      <c r="H26" s="27"/>
+      <c r="I26" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -2364,16 +2411,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -2382,19 +2429,19 @@
     </row>
     <row r="28" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12" t="s">
+      <c r="G28" s="14" t="s">
         <v>80</v>
+      </c>
+      <c r="H28" s="27"/>
+      <c r="I28" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -2403,17 +2450,17 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>81</v>
+      <c r="A29" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -2421,20 +2468,20 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>82</v>
+      <c r="A30" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12" t="s">
+      <c r="G30" s="14" t="s">
         <v>84</v>
+      </c>
+      <c r="H30" s="27"/>
+      <c r="I30" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -2443,17 +2490,17 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>85</v>
+      <c r="A31" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -2461,17 +2508,17 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>86</v>
+      <c r="A32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
@@ -2479,17 +2526,17 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>87</v>
+      <c r="A33" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
@@ -2497,20 +2544,20 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>88</v>
+      <c r="A34" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12" t="s">
-        <v>89</v>
+      <c r="G34" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="27"/>
+      <c r="I34" s="14" t="s">
+        <v>91</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -2519,17 +2566,17 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -2537,20 +2584,20 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>91</v>
+      <c r="A36" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12" t="s">
-        <v>92</v>
+      <c r="G36" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="27"/>
+      <c r="I36" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -2559,17 +2606,17 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>93</v>
+      <c r="A37" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
@@ -2577,17 +2624,17 @@
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>94</v>
+      <c r="A38" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -2595,17 +2642,17 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>95</v>
+      <c r="A39" s="22" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
@@ -2613,17 +2660,17 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>96</v>
+      <c r="A40" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="14"/>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -2651,7 +2698,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2720,12 +2767,12 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>105</v>
+      <c r="G3" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12" t="s">
-        <v>106</v>
+      <c r="I3" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2742,9 +2789,9 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -2760,9 +2807,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -2778,9 +2825,9 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -2796,9 +2843,9 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
+      <c r="G7" s="14"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -2814,9 +2861,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -2832,9 +2879,9 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="14"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -2850,9 +2897,9 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -2868,12 +2915,12 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
-        <v>107</v>
+      <c r="G11" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
-        <v>107</v>
+      <c r="I11" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -2890,9 +2937,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -2908,9 +2955,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -2926,16 +2973,16 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>48</v>
       </c>
@@ -2944,9 +2991,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="14" t="s">
+        <v>105</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -2962,9 +3013,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -2972,7 +3023,7 @@
       <c r="N16" s="11"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="11"/>
@@ -2980,9 +3031,9 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -2990,7 +3041,7 @@
       <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="11"/>
@@ -2998,9 +3049,9 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -3008,7 +3059,7 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="11"/>
@@ -3016,9 +3067,9 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -3026,7 +3077,7 @@
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="11"/>
@@ -3034,9 +3085,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -3044,7 +3095,7 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="11"/>
@@ -3052,9 +3103,9 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
@@ -3062,17 +3113,17 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>64</v>
+      <c r="A22" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="14"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -3080,17 +3131,17 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>66</v>
+      <c r="A23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="14"/>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -3098,17 +3149,17 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>68</v>
+      <c r="A24" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
@@ -3116,17 +3167,17 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>71</v>
+      <c r="A25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="14"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
@@ -3134,17 +3185,17 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>74</v>
+      <c r="A26" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="14"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -3153,16 +3204,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -3171,16 +3222,16 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -3188,17 +3239,17 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>81</v>
+      <c r="A29" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -3206,17 +3257,17 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>82</v>
+      <c r="A30" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
@@ -3224,17 +3275,17 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>85</v>
+      <c r="A31" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -3242,17 +3293,17 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>86</v>
+      <c r="A32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
@@ -3260,17 +3311,17 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>87</v>
+      <c r="A33" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
@@ -3278,17 +3329,17 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>88</v>
+      <c r="A34" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -3296,17 +3347,17 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -3314,17 +3365,17 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>91</v>
+      <c r="A36" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -3332,17 +3383,17 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>93</v>
+      <c r="A37" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
@@ -3350,17 +3401,21 @@
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>94</v>
+      <c r="A38" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -3368,17 +3423,17 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>95</v>
+      <c r="A39" s="22" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
@@ -3386,17 +3441,21 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>96</v>
+      <c r="A40" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -3424,7 +3483,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3493,9 +3552,13 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="14" t="s">
+        <v>109</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -3511,9 +3574,9 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -3529,9 +3592,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -3547,9 +3610,9 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -3565,9 +3628,9 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
+      <c r="G7" s="14"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -3583,9 +3646,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -3601,9 +3664,9 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="14"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -3619,9 +3682,9 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -3637,9 +3700,9 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -3655,9 +3718,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -3673,9 +3736,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -3691,16 +3754,16 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>48</v>
       </c>
@@ -3709,9 +3772,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="14" t="s">
+        <v>110</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -3727,9 +3794,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -3737,7 +3804,7 @@
       <c r="N16" s="11"/>
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="11"/>
@@ -3745,11 +3812,11 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="14" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -3757,7 +3824,7 @@
       <c r="N17" s="11"/>
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="11"/>
@@ -3765,11 +3832,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>53</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -3777,7 +3846,7 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="11"/>
@@ -3785,9 +3854,9 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -3795,7 +3864,7 @@
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="11"/>
@@ -3803,9 +3872,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -3813,7 +3882,7 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="11"/>
@@ -3821,9 +3890,9 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
@@ -3831,17 +3900,17 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>64</v>
+      <c r="A22" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="14"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -3849,17 +3918,21 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>66</v>
+      <c r="A23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -3867,17 +3940,17 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>68</v>
+      <c r="A24" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
@@ -3885,17 +3958,17 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>71</v>
+      <c r="A25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="14"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
@@ -3903,17 +3976,17 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>74</v>
+      <c r="A26" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="14"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -3922,16 +3995,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -3940,16 +4013,16 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -3957,17 +4030,17 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>81</v>
+      <c r="A29" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -3975,17 +4048,17 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>82</v>
+      <c r="A30" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
@@ -3993,17 +4066,17 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>85</v>
+      <c r="A31" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -4011,17 +4084,17 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>86</v>
+      <c r="A32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
@@ -4029,17 +4102,17 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>87</v>
+      <c r="A33" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
@@ -4047,17 +4120,17 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>88</v>
+      <c r="A34" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -4065,17 +4138,17 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -4083,17 +4156,17 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>91</v>
+      <c r="A36" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -4101,35 +4174,39 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>93</v>
+      <c r="A37" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>94</v>
+    <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -4137,35 +4214,39 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>95</v>
+      <c r="A39" s="22" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>96</v>
+    <row r="40" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -4193,7 +4274,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4262,9 +4343,9 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -4280,9 +4361,9 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -4298,9 +4379,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -4316,9 +4397,9 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -4334,9 +4415,9 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
+      <c r="G7" s="14"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -4352,9 +4433,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -4370,9 +4451,9 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="14"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -4388,9 +4469,9 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -4406,9 +4487,9 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -4424,9 +4505,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -4442,9 +4523,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -4460,9 +4541,9 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -4478,9 +4559,9 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -4496,9 +4577,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -4506,7 +4587,7 @@
       <c r="N16" s="11"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="11"/>
@@ -4514,9 +4595,9 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -4524,7 +4605,7 @@
       <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="11"/>
@@ -4532,9 +4613,9 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -4542,7 +4623,7 @@
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="11"/>
@@ -4550,9 +4631,9 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -4560,7 +4641,7 @@
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="11"/>
@@ -4568,9 +4649,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -4578,7 +4659,7 @@
       <c r="N20" s="11"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="11"/>
@@ -4586,9 +4667,9 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
@@ -4596,17 +4677,17 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>64</v>
+      <c r="A22" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="14"/>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -4614,17 +4695,17 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>66</v>
+      <c r="A23" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="14"/>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -4632,17 +4713,17 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>68</v>
+      <c r="A24" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
@@ -4650,17 +4731,17 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>71</v>
+      <c r="A25" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="14"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
@@ -4668,17 +4749,17 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>74</v>
+      <c r="A26" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="14"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -4687,16 +4768,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -4705,16 +4786,16 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -4722,17 +4803,17 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>81</v>
+      <c r="A29" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -4740,17 +4821,17 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>82</v>
+      <c r="A30" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
@@ -4758,17 +4839,17 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>85</v>
+      <c r="A31" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="14"/>
       <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -4776,17 +4857,17 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>86</v>
+      <c r="A32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="14"/>
       <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
@@ -4794,17 +4875,17 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>87</v>
+      <c r="A33" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
@@ -4812,17 +4893,17 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>88</v>
+      <c r="A34" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -4830,17 +4911,17 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -4848,17 +4929,17 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>91</v>
+      <c r="A36" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -4866,17 +4947,17 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>93</v>
+      <c r="A37" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
@@ -4884,17 +4965,17 @@
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>94</v>
+      <c r="A38" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -4902,17 +4983,17 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>95</v>
+      <c r="A39" s="22" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
@@ -4920,17 +5001,17 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>96</v>
+      <c r="A40" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="14"/>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>

--- a/public/管理口径原因分析默认模版/常州项目部.xlsx
+++ b/public/管理口径原因分析默认模版/常州项目部.xlsx
@@ -10,9 +10,9 @@
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
     <sheet sheetId="4" name="常州酒店" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="江苏常州酒店能源转售" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="江苏常州销售分公司配餐项目" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="常州酒店项目部销售费用" state="visible" r:id="rId9"/>
+    <sheet sheetId="5" name="常州酒店能源" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="常州配餐" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="常州酒店销售费" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -39,13 +39,13 @@
     <t>常州酒店</t>
   </si>
   <si>
-    <t>江苏常州酒店能源转售</t>
-  </si>
-  <si>
-    <t>江苏常州销售分公司配餐项目</t>
-  </si>
-  <si>
-    <t>常州酒店项目部销售费用</t>
+    <t>常州酒店能源</t>
+  </si>
+  <si>
+    <t>常州配餐</t>
+  </si>
+  <si>
+    <t>常州酒店销售费</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -342,7 +342,7 @@
     <t>常州酒店预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏常州酒店能源转售预算执行分析（2026年08月）</t>
+    <t>常州酒店能源预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>能源转售收入为桔子和影音酒店的合作经营加入影响。</t>
@@ -363,7 +363,7 @@
     <t xml:space="preserve">收入带来的利润影响 </t>
   </si>
   <si>
-    <t>江苏常州销售分公司配餐项目预算执行分析（2026年08月）</t>
+    <t>常州配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>增加服务费</t>
@@ -387,7 +387,7 @@
     <t>人工成本增加影响利润</t>
   </si>
   <si>
-    <t>常州酒店项目部销售费用预算执行分析（2026年08月）</t>
+    <t>常州酒店销售费预算执行分析（2026年08月）</t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'江苏常州酒店能源转售'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'常州酒店能源'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'江苏常州销售分公司配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'常州配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -976,7 +976,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'常州酒店项目部销售费用'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'常州酒店销售费'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
